--- a/00_Running_Transaction_Listing.xlsx
+++ b/00_Running_Transaction_Listing.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13891" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13976" uniqueCount="2161">
   <si>
     <t xml:space="preserve">Parks 4090000 NA Review — Running Transaction Listing</t>
   </si>
@@ -199,7 +199,7 @@
     <t xml:space="preserve">73211 Minor Contracts (below $20,000)</t>
   </si>
   <si>
-    <t xml:space="preserve">58%</t>
+    <t xml:space="preserve">55%</t>
   </si>
   <si>
     <t xml:space="preserve">0 / 7</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">0 / 48</t>
   </si>
   <si>
-    <t xml:space="preserve">0 / 66 / 48</t>
+    <t xml:space="preserve">0 / 66 / 54</t>
   </si>
   <si>
     <t xml:space="preserve">73541 Conferences &amp; Seminar Fees</t>
@@ -5608,7 +5608,7 @@
     <t xml:space="preserve">Woolworths Online-General Expenses-Purchase Card Reconciliat</t>
   </si>
   <si>
-    <t xml:space="preserve">NA 73211 Minor Contracts (below $20,000) — line-level review (114 lines, $236,378.27 ex-GST)</t>
+    <t xml:space="preserve">NA 73211 Minor Contracts (below $20,000) — line-level review (120 lines, $267,532.19 ex-GST)</t>
   </si>
   <si>
     <t xml:space="preserve">73211</t>
@@ -6282,6 +6282,48 @@
   </si>
   <si>
     <t xml:space="preserve">F2 candidate 73211&gt;73212 (above the $20,000 floor on its face); INCON ABR sighted 11-Jun (active, GST reg; NOTE-tier young-entity concerns). New reading: materials supply, not contract services - arguably a stores/materials question. Held un-instructed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-0356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote Q261.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export). F2 candidate 73211&gt;73212: $24,340 sits above the $20,000 minor-contracts floor on its face (Destination Trails Mountain Bike Trails series). Supporting doc received this session, archived _Sources_16-Jun-2026/NA73211_ReExport_17-Jun/, NOT yet worked. Held un-instructed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00031242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export), Community Planting Program standing order. Supporting doc received, archived raw, not yet worked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INV-1407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export), ParkCare standing order. Supporting doc received, archived raw, not yet worked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00031269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export), Bushcare Program standing order. Supporting doc received, archived raw, not yet worked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00001168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export), Cemeteries standing order. Supporting doc received, archived raw, not yet worked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00061080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New P12 line (17-Jun re-export), Free Trees Program standing order. Supporting doc received, archived raw, not yet worked.</t>
   </si>
   <si>
     <t xml:space="preserve">NA 73541 Conferences &amp; Seminar Fees — line-level review (6 lines, $642.14 ex-GST)</t>
@@ -6763,7 +6805,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6889,10 +6931,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7614,10 +7652,10 @@
         <v>49</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>236378.27</v>
+        <v>267532.19</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>50</v>
@@ -7638,7 +7676,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>55</v>
       </c>
@@ -7667,7 +7705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>56</v>
       </c>
@@ -7696,7 +7734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>57</v>
       </c>
@@ -7725,7 +7763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>58</v>
       </c>
@@ -7754,17 +7792,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">SUM(B4:B17)</f>
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">SUM(C4:C17)</f>
-        <v>403298.5</v>
+        <v>434452.42</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -14922,57 +14960,57 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V116"/>
+  <dimension ref="A1:V122"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="20" t="s">
         <v>1852</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -15042,7 +15080,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15083,7 +15121,7 @@
       <c r="N3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="33"/>
+      <c r="O3" s="32"/>
       <c r="P3" s="26" t="s">
         <v>75</v>
       </c>
@@ -15102,7 +15140,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15143,7 +15181,7 @@
       <c r="N4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="26" t="s">
         <v>75</v>
       </c>
@@ -15162,7 +15200,7 @@
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15201,7 +15239,7 @@
       <c r="N5" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="33"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="22" t="s">
         <v>77</v>
       </c>
@@ -15220,7 +15258,7 @@
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15261,7 +15299,7 @@
       <c r="N6" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O6" s="33"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="26" t="s">
         <v>75</v>
       </c>
@@ -15280,7 +15318,7 @@
       <c r="U6" s="23"/>
       <c r="V6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15319,7 +15357,7 @@
       <c r="N7" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="22" t="s">
         <v>77</v>
       </c>
@@ -15338,7 +15376,7 @@
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15377,7 +15415,7 @@
       <c r="N8" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="33"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="26" t="s">
         <v>75</v>
       </c>
@@ -15396,7 +15434,7 @@
       <c r="U8" s="23"/>
       <c r="V8" s="23"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15435,7 +15473,7 @@
       <c r="N9" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="33"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="26" t="s">
         <v>75</v>
       </c>
@@ -15454,7 +15492,7 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15493,7 +15531,7 @@
       <c r="N10" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O10" s="33"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="21" t="s">
         <v>81</v>
       </c>
@@ -15512,7 +15550,7 @@
       <c r="U10" s="23"/>
       <c r="V10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15553,7 +15591,7 @@
       <c r="N11" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="33"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="22" t="s">
         <v>77</v>
       </c>
@@ -15572,7 +15610,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15611,7 +15649,7 @@
       <c r="N12" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O12" s="33"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="21" t="s">
         <v>81</v>
       </c>
@@ -15630,7 +15668,7 @@
       <c r="U12" s="23"/>
       <c r="V12" s="23"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15669,7 +15707,7 @@
       <c r="N13" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O13" s="33"/>
+      <c r="O13" s="32"/>
       <c r="P13" s="21" t="s">
         <v>81</v>
       </c>
@@ -15688,7 +15726,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15729,7 +15767,7 @@
       <c r="N14" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="33"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="26" t="s">
         <v>75</v>
       </c>
@@ -15748,7 +15786,7 @@
       <c r="U14" s="23"/>
       <c r="V14" s="23"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15787,7 +15825,7 @@
       <c r="N15" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O15" s="33"/>
+      <c r="O15" s="32"/>
       <c r="P15" s="21" t="s">
         <v>81</v>
       </c>
@@ -15806,7 +15844,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15847,7 +15885,7 @@
       <c r="N16" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O16" s="33"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="21" t="s">
         <v>81</v>
       </c>
@@ -15866,7 +15904,7 @@
       <c r="U16" s="23"/>
       <c r="V16" s="23"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>1853</v>
       </c>
@@ -15905,7 +15943,7 @@
       <c r="N17" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O17" s="33"/>
+      <c r="O17" s="32"/>
       <c r="P17" s="21" t="s">
         <v>81</v>
       </c>
@@ -15924,7 +15962,7 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
         <v>1853</v>
       </c>
@@ -15965,7 +16003,7 @@
       <c r="N18" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O18" s="33"/>
+      <c r="O18" s="32"/>
       <c r="P18" s="26" t="s">
         <v>75</v>
       </c>
@@ -15984,7 +16022,7 @@
       <c r="U18" s="23"/>
       <c r="V18" s="23"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16025,7 +16063,7 @@
       <c r="N19" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O19" s="33"/>
+      <c r="O19" s="32"/>
       <c r="P19" s="26" t="s">
         <v>75</v>
       </c>
@@ -16044,7 +16082,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16085,7 +16123,7 @@
       <c r="N20" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O20" s="33"/>
+      <c r="O20" s="32"/>
       <c r="P20" s="26" t="s">
         <v>75</v>
       </c>
@@ -16104,7 +16142,7 @@
       <c r="U20" s="23"/>
       <c r="V20" s="23"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16145,7 +16183,7 @@
       <c r="N21" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O21" s="33"/>
+      <c r="O21" s="32"/>
       <c r="P21" s="26" t="s">
         <v>75</v>
       </c>
@@ -16164,7 +16202,7 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16205,7 +16243,7 @@
       <c r="N22" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O22" s="33"/>
+      <c r="O22" s="32"/>
       <c r="P22" s="26" t="s">
         <v>75</v>
       </c>
@@ -16224,7 +16262,7 @@
       <c r="U22" s="23"/>
       <c r="V22" s="23"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16263,7 +16301,7 @@
       <c r="N23" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O23" s="33"/>
+      <c r="O23" s="32"/>
       <c r="P23" s="26" t="s">
         <v>75</v>
       </c>
@@ -16282,7 +16320,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16323,7 +16361,7 @@
       <c r="N24" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O24" s="33"/>
+      <c r="O24" s="32"/>
       <c r="P24" s="26" t="s">
         <v>75</v>
       </c>
@@ -16342,7 +16380,7 @@
       <c r="U24" s="23"/>
       <c r="V24" s="23"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16383,7 +16421,7 @@
       <c r="N25" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O25" s="33"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="26" t="s">
         <v>75</v>
       </c>
@@ -16402,7 +16440,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16443,7 +16481,7 @@
       <c r="N26" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O26" s="33"/>
+      <c r="O26" s="32"/>
       <c r="P26" s="26" t="s">
         <v>75</v>
       </c>
@@ -16462,7 +16500,7 @@
       <c r="U26" s="23"/>
       <c r="V26" s="23"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16503,7 +16541,7 @@
       <c r="N27" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O27" s="33"/>
+      <c r="O27" s="32"/>
       <c r="P27" s="26" t="s">
         <v>75</v>
       </c>
@@ -16522,7 +16560,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16561,7 +16599,7 @@
       <c r="N28" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O28" s="33"/>
+      <c r="O28" s="32"/>
       <c r="P28" s="21" t="s">
         <v>81</v>
       </c>
@@ -16580,7 +16618,7 @@
       <c r="U28" s="23"/>
       <c r="V28" s="23"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16621,7 +16659,7 @@
       <c r="N29" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O29" s="33"/>
+      <c r="O29" s="32"/>
       <c r="P29" s="26" t="s">
         <v>75</v>
       </c>
@@ -16640,7 +16678,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16681,7 +16719,7 @@
       <c r="N30" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O30" s="33"/>
+      <c r="O30" s="32"/>
       <c r="P30" s="26" t="s">
         <v>75</v>
       </c>
@@ -16700,7 +16738,7 @@
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16739,7 +16777,7 @@
       <c r="N31" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O31" s="33"/>
+      <c r="O31" s="32"/>
       <c r="P31" s="21" t="s">
         <v>81</v>
       </c>
@@ -16758,7 +16796,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16797,7 +16835,7 @@
       <c r="N32" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O32" s="33"/>
+      <c r="O32" s="32"/>
       <c r="P32" s="21" t="s">
         <v>81</v>
       </c>
@@ -16816,7 +16854,7 @@
       <c r="U32" s="23"/>
       <c r="V32" s="23"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16857,7 +16895,7 @@
       <c r="N33" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O33" s="33"/>
+      <c r="O33" s="32"/>
       <c r="P33" s="26" t="s">
         <v>75</v>
       </c>
@@ -16876,7 +16914,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
         <v>1853</v>
       </c>
@@ -16919,7 +16957,7 @@
       <c r="N34" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O34" s="33"/>
+      <c r="O34" s="32"/>
       <c r="P34" s="22" t="s">
         <v>77</v>
       </c>
@@ -16938,7 +16976,7 @@
       <c r="U34" s="23"/>
       <c r="V34" s="23"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>1853</v>
       </c>
@@ -16977,7 +17015,7 @@
       <c r="N35" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O35" s="33"/>
+      <c r="O35" s="32"/>
       <c r="P35" s="21" t="s">
         <v>81</v>
       </c>
@@ -16996,7 +17034,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17037,7 +17075,7 @@
       <c r="N36" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O36" s="33"/>
+      <c r="O36" s="32"/>
       <c r="P36" s="26" t="s">
         <v>75</v>
       </c>
@@ -17056,7 +17094,7 @@
       <c r="U36" s="23"/>
       <c r="V36" s="23"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17095,7 +17133,7 @@
       <c r="N37" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O37" s="33"/>
+      <c r="O37" s="32"/>
       <c r="P37" s="21" t="s">
         <v>81</v>
       </c>
@@ -17114,7 +17152,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17153,7 +17191,7 @@
       <c r="N38" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O38" s="33"/>
+      <c r="O38" s="32"/>
       <c r="P38" s="21" t="s">
         <v>81</v>
       </c>
@@ -17172,7 +17210,7 @@
       <c r="U38" s="23"/>
       <c r="V38" s="23"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17213,7 +17251,7 @@
       <c r="N39" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O39" s="33"/>
+      <c r="O39" s="32"/>
       <c r="P39" s="26" t="s">
         <v>75</v>
       </c>
@@ -17232,7 +17270,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17273,7 +17311,7 @@
       <c r="N40" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O40" s="33"/>
+      <c r="O40" s="32"/>
       <c r="P40" s="26" t="s">
         <v>75</v>
       </c>
@@ -17292,7 +17330,7 @@
       <c r="U40" s="23"/>
       <c r="V40" s="23"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17331,7 +17369,7 @@
       <c r="N41" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O41" s="33"/>
+      <c r="O41" s="32"/>
       <c r="P41" s="21" t="s">
         <v>81</v>
       </c>
@@ -17350,7 +17388,7 @@
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17389,7 +17427,7 @@
       <c r="N42" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O42" s="33"/>
+      <c r="O42" s="32"/>
       <c r="P42" s="21" t="s">
         <v>81</v>
       </c>
@@ -17408,7 +17446,7 @@
       <c r="U42" s="23"/>
       <c r="V42" s="23"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17447,7 +17485,7 @@
       <c r="N43" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O43" s="33"/>
+      <c r="O43" s="32"/>
       <c r="P43" s="21" t="s">
         <v>81</v>
       </c>
@@ -17466,7 +17504,7 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17505,7 +17543,7 @@
       <c r="N44" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O44" s="33"/>
+      <c r="O44" s="32"/>
       <c r="P44" s="21" t="s">
         <v>81</v>
       </c>
@@ -17524,7 +17562,7 @@
       <c r="U44" s="23"/>
       <c r="V44" s="23"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17563,7 +17601,7 @@
       <c r="N45" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O45" s="33"/>
+      <c r="O45" s="32"/>
       <c r="P45" s="21" t="s">
         <v>81</v>
       </c>
@@ -17582,7 +17620,7 @@
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17623,7 +17661,7 @@
       <c r="N46" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O46" s="33"/>
+      <c r="O46" s="32"/>
       <c r="P46" s="22" t="s">
         <v>77</v>
       </c>
@@ -17642,7 +17680,7 @@
       <c r="U46" s="23"/>
       <c r="V46" s="23"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17681,7 +17719,7 @@
       <c r="N47" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O47" s="33"/>
+      <c r="O47" s="32"/>
       <c r="P47" s="21" t="s">
         <v>81</v>
       </c>
@@ -17700,7 +17738,7 @@
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17741,7 +17779,7 @@
       <c r="N48" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O48" s="33"/>
+      <c r="O48" s="32"/>
       <c r="P48" s="26" t="s">
         <v>75</v>
       </c>
@@ -17760,7 +17798,7 @@
       <c r="U48" s="23"/>
       <c r="V48" s="23"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17799,7 +17837,7 @@
       <c r="N49" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O49" s="33"/>
+      <c r="O49" s="32"/>
       <c r="P49" s="21" t="s">
         <v>81</v>
       </c>
@@ -17818,7 +17856,7 @@
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17857,7 +17895,7 @@
       <c r="N50" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O50" s="33"/>
+      <c r="O50" s="32"/>
       <c r="P50" s="21" t="s">
         <v>81</v>
       </c>
@@ -17876,7 +17914,7 @@
       <c r="U50" s="23"/>
       <c r="V50" s="23"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
         <v>1853</v>
       </c>
@@ -17915,7 +17953,7 @@
       <c r="N51" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O51" s="33"/>
+      <c r="O51" s="32"/>
       <c r="P51" s="21" t="s">
         <v>81</v>
       </c>
@@ -17934,7 +17972,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="s">
         <v>1853</v>
       </c>
@@ -17973,7 +18011,7 @@
       <c r="N52" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O52" s="33"/>
+      <c r="O52" s="32"/>
       <c r="P52" s="21" t="s">
         <v>81</v>
       </c>
@@ -17992,7 +18030,7 @@
       <c r="U52" s="23"/>
       <c r="V52" s="23"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18033,7 +18071,7 @@
       <c r="N53" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O53" s="33"/>
+      <c r="O53" s="32"/>
       <c r="P53" s="21" t="s">
         <v>81</v>
       </c>
@@ -18052,7 +18090,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18093,7 +18131,7 @@
       <c r="N54" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O54" s="33"/>
+      <c r="O54" s="32"/>
       <c r="P54" s="22" t="s">
         <v>77</v>
       </c>
@@ -18112,7 +18150,7 @@
       <c r="U54" s="23"/>
       <c r="V54" s="23"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18151,7 +18189,7 @@
       <c r="N55" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O55" s="33"/>
+      <c r="O55" s="32"/>
       <c r="P55" s="21" t="s">
         <v>81</v>
       </c>
@@ -18170,7 +18208,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18207,7 +18245,7 @@
       <c r="N56" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O56" s="33"/>
+      <c r="O56" s="32"/>
       <c r="P56" s="21" t="s">
         <v>81</v>
       </c>
@@ -18226,7 +18264,7 @@
       <c r="U56" s="23"/>
       <c r="V56" s="23"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18265,7 +18303,7 @@
       <c r="N57" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O57" s="33"/>
+      <c r="O57" s="32"/>
       <c r="P57" s="21" t="s">
         <v>81</v>
       </c>
@@ -18284,7 +18322,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18323,7 +18361,7 @@
       <c r="N58" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O58" s="33"/>
+      <c r="O58" s="32"/>
       <c r="P58" s="21" t="s">
         <v>81</v>
       </c>
@@ -18342,7 +18380,7 @@
       <c r="U58" s="23"/>
       <c r="V58" s="23"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18381,7 +18419,7 @@
       <c r="N59" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O59" s="33"/>
+      <c r="O59" s="32"/>
       <c r="P59" s="21" t="s">
         <v>81</v>
       </c>
@@ -18400,7 +18438,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18439,7 +18477,7 @@
       <c r="N60" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O60" s="33"/>
+      <c r="O60" s="32"/>
       <c r="P60" s="21" t="s">
         <v>81</v>
       </c>
@@ -18458,7 +18496,7 @@
       <c r="U60" s="23"/>
       <c r="V60" s="23"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18499,7 +18537,7 @@
       <c r="N61" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O61" s="33"/>
+      <c r="O61" s="32"/>
       <c r="P61" s="22" t="s">
         <v>77</v>
       </c>
@@ -18518,7 +18556,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18559,7 +18597,7 @@
       <c r="N62" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O62" s="33"/>
+      <c r="O62" s="32"/>
       <c r="P62" s="22" t="s">
         <v>77</v>
       </c>
@@ -18578,7 +18616,7 @@
       <c r="U62" s="23"/>
       <c r="V62" s="23"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18617,7 +18655,7 @@
       <c r="N63" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O63" s="33"/>
+      <c r="O63" s="32"/>
       <c r="P63" s="21" t="s">
         <v>81</v>
       </c>
@@ -18636,7 +18674,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18675,7 +18713,7 @@
       <c r="N64" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O64" s="33"/>
+      <c r="O64" s="32"/>
       <c r="P64" s="21" t="s">
         <v>81</v>
       </c>
@@ -18694,7 +18732,7 @@
       <c r="U64" s="23"/>
       <c r="V64" s="23"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18735,7 +18773,7 @@
       <c r="N65" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O65" s="33"/>
+      <c r="O65" s="32"/>
       <c r="P65" s="26" t="s">
         <v>75</v>
       </c>
@@ -18754,7 +18792,7 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18795,7 +18833,7 @@
       <c r="N66" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O66" s="33"/>
+      <c r="O66" s="32"/>
       <c r="P66" s="22" t="s">
         <v>77</v>
       </c>
@@ -18814,7 +18852,7 @@
       <c r="U66" s="23"/>
       <c r="V66" s="23"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18855,7 +18893,7 @@
       <c r="N67" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O67" s="33"/>
+      <c r="O67" s="32"/>
       <c r="P67" s="22" t="s">
         <v>77</v>
       </c>
@@ -18874,7 +18912,7 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="s">
         <v>1853</v>
       </c>
@@ -18915,7 +18953,7 @@
       <c r="N68" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O68" s="33"/>
+      <c r="O68" s="32"/>
       <c r="P68" s="22" t="s">
         <v>77</v>
       </c>
@@ -18934,7 +18972,7 @@
       <c r="U68" s="23"/>
       <c r="V68" s="23"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
         <v>1853</v>
       </c>
@@ -18975,7 +19013,7 @@
       <c r="N69" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O69" s="33"/>
+      <c r="O69" s="32"/>
       <c r="P69" s="22" t="s">
         <v>77</v>
       </c>
@@ -18994,7 +19032,7 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19035,7 +19073,7 @@
       <c r="N70" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O70" s="33"/>
+      <c r="O70" s="32"/>
       <c r="P70" s="22" t="s">
         <v>77</v>
       </c>
@@ -19054,7 +19092,7 @@
       <c r="U70" s="23"/>
       <c r="V70" s="23"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19095,7 +19133,7 @@
       <c r="N71" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O71" s="33"/>
+      <c r="O71" s="32"/>
       <c r="P71" s="22" t="s">
         <v>77</v>
       </c>
@@ -19114,7 +19152,7 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19155,7 +19193,7 @@
       <c r="N72" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O72" s="33"/>
+      <c r="O72" s="32"/>
       <c r="P72" s="22" t="s">
         <v>77</v>
       </c>
@@ -19174,7 +19212,7 @@
       <c r="U72" s="23"/>
       <c r="V72" s="23"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19213,7 +19251,7 @@
       <c r="N73" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O73" s="33"/>
+      <c r="O73" s="32"/>
       <c r="P73" s="21" t="s">
         <v>81</v>
       </c>
@@ -19232,7 +19270,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19273,7 +19311,7 @@
       <c r="N74" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O74" s="33"/>
+      <c r="O74" s="32"/>
       <c r="P74" s="22" t="s">
         <v>77</v>
       </c>
@@ -19292,7 +19330,7 @@
       <c r="U74" s="23"/>
       <c r="V74" s="23"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19331,7 +19369,7 @@
       <c r="N75" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O75" s="33"/>
+      <c r="O75" s="32"/>
       <c r="P75" s="21" t="s">
         <v>81</v>
       </c>
@@ -19350,7 +19388,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19391,7 +19429,7 @@
       <c r="N76" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O76" s="33"/>
+      <c r="O76" s="32"/>
       <c r="P76" s="22" t="s">
         <v>77</v>
       </c>
@@ -19410,7 +19448,7 @@
       <c r="U76" s="23"/>
       <c r="V76" s="23"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19451,7 +19489,7 @@
       <c r="N77" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O77" s="33"/>
+      <c r="O77" s="32"/>
       <c r="P77" s="22" t="s">
         <v>77</v>
       </c>
@@ -19470,7 +19508,7 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19509,7 +19547,7 @@
       <c r="N78" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O78" s="33"/>
+      <c r="O78" s="32"/>
       <c r="P78" s="21" t="s">
         <v>81</v>
       </c>
@@ -19528,7 +19566,7 @@
       <c r="U78" s="23"/>
       <c r="V78" s="23"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19569,7 +19607,7 @@
       <c r="N79" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O79" s="33"/>
+      <c r="O79" s="32"/>
       <c r="P79" s="21" t="s">
         <v>81</v>
       </c>
@@ -19588,7 +19626,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19629,7 +19667,7 @@
       <c r="N80" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O80" s="33"/>
+      <c r="O80" s="32"/>
       <c r="P80" s="21" t="s">
         <v>81</v>
       </c>
@@ -19648,7 +19686,7 @@
       <c r="U80" s="23"/>
       <c r="V80" s="23"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19687,7 +19725,7 @@
       <c r="N81" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O81" s="33"/>
+      <c r="O81" s="32"/>
       <c r="P81" s="21" t="s">
         <v>81</v>
       </c>
@@ -19706,7 +19744,7 @@
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19745,7 +19783,7 @@
       <c r="N82" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O82" s="33"/>
+      <c r="O82" s="32"/>
       <c r="P82" s="21" t="s">
         <v>81</v>
       </c>
@@ -19764,7 +19802,7 @@
       <c r="U82" s="23"/>
       <c r="V82" s="23"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19803,7 +19841,7 @@
       <c r="N83" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O83" s="33"/>
+      <c r="O83" s="32"/>
       <c r="P83" s="22" t="s">
         <v>77</v>
       </c>
@@ -19822,7 +19860,7 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19861,7 +19899,7 @@
       <c r="N84" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O84" s="33"/>
+      <c r="O84" s="32"/>
       <c r="P84" s="21" t="s">
         <v>81</v>
       </c>
@@ -19880,7 +19918,7 @@
       <c r="U84" s="23"/>
       <c r="V84" s="23"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
         <v>1853</v>
       </c>
@@ -19921,7 +19959,7 @@
       <c r="N85" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O85" s="33"/>
+      <c r="O85" s="32"/>
       <c r="P85" s="22" t="s">
         <v>77</v>
       </c>
@@ -19940,7 +19978,7 @@
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="23" t="s">
         <v>1853</v>
       </c>
@@ -19981,7 +20019,7 @@
       <c r="N86" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O86" s="33"/>
+      <c r="O86" s="32"/>
       <c r="P86" s="21" t="s">
         <v>81</v>
       </c>
@@ -20000,7 +20038,7 @@
       <c r="U86" s="23"/>
       <c r="V86" s="23"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20039,7 +20077,7 @@
       <c r="N87" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O87" s="33"/>
+      <c r="O87" s="32"/>
       <c r="P87" s="21" t="s">
         <v>81</v>
       </c>
@@ -20058,7 +20096,7 @@
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20099,7 +20137,7 @@
       <c r="N88" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O88" s="33"/>
+      <c r="O88" s="32"/>
       <c r="P88" s="22" t="s">
         <v>77</v>
       </c>
@@ -20118,7 +20156,7 @@
       <c r="U88" s="23"/>
       <c r="V88" s="23"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20159,7 +20197,7 @@
       <c r="N89" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O89" s="33"/>
+      <c r="O89" s="32"/>
       <c r="P89" s="22" t="s">
         <v>77</v>
       </c>
@@ -20178,7 +20216,7 @@
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20219,7 +20257,7 @@
       <c r="N90" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O90" s="33"/>
+      <c r="O90" s="32"/>
       <c r="P90" s="22" t="s">
         <v>77</v>
       </c>
@@ -20238,7 +20276,7 @@
       <c r="U90" s="23"/>
       <c r="V90" s="23"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20279,7 +20317,7 @@
       <c r="N91" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O91" s="33"/>
+      <c r="O91" s="32"/>
       <c r="P91" s="22" t="s">
         <v>77</v>
       </c>
@@ -20298,7 +20336,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20339,7 +20377,7 @@
       <c r="N92" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O92" s="33"/>
+      <c r="O92" s="32"/>
       <c r="P92" s="26" t="s">
         <v>75</v>
       </c>
@@ -20358,7 +20396,7 @@
       <c r="U92" s="23"/>
       <c r="V92" s="23"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20399,7 +20437,7 @@
       <c r="N93" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O93" s="33"/>
+      <c r="O93" s="32"/>
       <c r="P93" s="22" t="s">
         <v>77</v>
       </c>
@@ -20418,7 +20456,7 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20459,7 +20497,7 @@
       <c r="N94" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O94" s="33"/>
+      <c r="O94" s="32"/>
       <c r="P94" s="26" t="s">
         <v>75</v>
       </c>
@@ -20478,7 +20516,7 @@
       <c r="U94" s="23"/>
       <c r="V94" s="23"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20519,7 +20557,7 @@
       <c r="N95" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O95" s="33"/>
+      <c r="O95" s="32"/>
       <c r="P95" s="22" t="s">
         <v>77</v>
       </c>
@@ -20538,7 +20576,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20579,7 +20617,7 @@
       <c r="N96" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O96" s="33"/>
+      <c r="O96" s="32"/>
       <c r="P96" s="21" t="s">
         <v>81</v>
       </c>
@@ -20598,7 +20636,7 @@
       <c r="U96" s="23"/>
       <c r="V96" s="23"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20637,7 +20675,7 @@
       <c r="N97" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O97" s="33"/>
+      <c r="O97" s="32"/>
       <c r="P97" s="21" t="s">
         <v>81</v>
       </c>
@@ -20656,7 +20694,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20695,7 +20733,7 @@
       <c r="N98" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O98" s="33"/>
+      <c r="O98" s="32"/>
       <c r="P98" s="26" t="s">
         <v>75</v>
       </c>
@@ -20714,7 +20752,7 @@
       <c r="U98" s="23"/>
       <c r="V98" s="23"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20753,7 +20791,7 @@
       <c r="N99" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O99" s="33"/>
+      <c r="O99" s="32"/>
       <c r="P99" s="26" t="s">
         <v>75</v>
       </c>
@@ -20772,7 +20810,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20813,7 +20851,7 @@
       <c r="N100" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O100" s="33"/>
+      <c r="O100" s="32"/>
       <c r="P100" s="26" t="s">
         <v>75</v>
       </c>
@@ -20832,7 +20870,7 @@
       <c r="U100" s="23"/>
       <c r="V100" s="23"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20873,7 +20911,7 @@
       <c r="N101" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O101" s="33"/>
+      <c r="O101" s="32"/>
       <c r="P101" s="22" t="s">
         <v>77</v>
       </c>
@@ -20892,7 +20930,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="23" t="s">
         <v>1853</v>
       </c>
@@ -20931,7 +20969,7 @@
       <c r="N102" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O102" s="33"/>
+      <c r="O102" s="32"/>
       <c r="P102" s="21" t="s">
         <v>81</v>
       </c>
@@ -20950,7 +20988,7 @@
       <c r="U102" s="23"/>
       <c r="V102" s="23"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
         <v>1853</v>
       </c>
@@ -20991,7 +21029,7 @@
       <c r="N103" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O103" s="33"/>
+      <c r="O103" s="32"/>
       <c r="P103" s="21" t="s">
         <v>81</v>
       </c>
@@ -21010,7 +21048,7 @@
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21051,7 +21089,7 @@
       <c r="N104" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O104" s="33"/>
+      <c r="O104" s="32"/>
       <c r="P104" s="26" t="s">
         <v>75</v>
       </c>
@@ -21070,7 +21108,7 @@
       <c r="U104" s="23"/>
       <c r="V104" s="23"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21109,7 +21147,7 @@
       <c r="N105" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O105" s="33"/>
+      <c r="O105" s="32"/>
       <c r="P105" s="21" t="s">
         <v>81</v>
       </c>
@@ -21128,7 +21166,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21169,7 +21207,7 @@
       <c r="N106" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O106" s="33"/>
+      <c r="O106" s="32"/>
       <c r="P106" s="22" t="s">
         <v>77</v>
       </c>
@@ -21188,7 +21226,7 @@
       <c r="U106" s="23"/>
       <c r="V106" s="23"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21227,7 +21265,7 @@
       <c r="N107" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O107" s="33"/>
+      <c r="O107" s="32"/>
       <c r="P107" s="21" t="s">
         <v>81</v>
       </c>
@@ -21246,7 +21284,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21287,7 +21325,7 @@
       <c r="N108" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O108" s="33"/>
+      <c r="O108" s="32"/>
       <c r="P108" s="26" t="s">
         <v>75</v>
       </c>
@@ -21306,7 +21344,7 @@
       <c r="U108" s="23"/>
       <c r="V108" s="23"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21347,7 +21385,7 @@
       <c r="N109" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O109" s="33"/>
+      <c r="O109" s="32"/>
       <c r="P109" s="22" t="s">
         <v>77</v>
       </c>
@@ -21366,7 +21404,7 @@
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21407,7 +21445,7 @@
       <c r="N110" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O110" s="33"/>
+      <c r="O110" s="32"/>
       <c r="P110" s="26" t="s">
         <v>75</v>
       </c>
@@ -21426,7 +21464,7 @@
       <c r="U110" s="23"/>
       <c r="V110" s="23"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21467,7 +21505,7 @@
       <c r="N111" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O111" s="33"/>
+      <c r="O111" s="32"/>
       <c r="P111" s="26" t="s">
         <v>75</v>
       </c>
@@ -21486,7 +21524,7 @@
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21525,7 +21563,7 @@
       <c r="N112" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O112" s="33"/>
+      <c r="O112" s="32"/>
       <c r="P112" s="21" t="s">
         <v>81</v>
       </c>
@@ -21544,7 +21582,7 @@
       <c r="U112" s="23"/>
       <c r="V112" s="23"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21585,7 +21623,7 @@
       <c r="N113" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O113" s="33"/>
+      <c r="O113" s="32"/>
       <c r="P113" s="22" t="s">
         <v>77</v>
       </c>
@@ -21604,7 +21642,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21645,7 +21683,7 @@
       <c r="N114" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O114" s="33"/>
+      <c r="O114" s="32"/>
       <c r="P114" s="22" t="s">
         <v>77</v>
       </c>
@@ -21664,7 +21702,7 @@
       <c r="U114" s="23"/>
       <c r="V114" s="23"/>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
         <v>1853</v>
       </c>
@@ -21705,7 +21743,7 @@
       <c r="N115" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O115" s="33"/>
+      <c r="O115" s="32"/>
       <c r="P115" s="22" t="s">
         <v>77</v>
       </c>
@@ -21724,7 +21762,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="23" t="s">
         <v>1853</v>
       </c>
@@ -21765,7 +21803,7 @@
       <c r="N116" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O116" s="33"/>
+      <c r="O116" s="32"/>
       <c r="P116" s="22" t="s">
         <v>77</v>
       </c>
@@ -21783,6 +21821,356 @@
       </c>
       <c r="U116" s="23"/>
       <c r="V116" s="23"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B117" s="24" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D117" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E117" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F117" s="24" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G117" s="23" t="s">
+        <v>2077</v>
+      </c>
+      <c r="H117" s="23" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I117" s="23"/>
+      <c r="J117" s="23" t="s">
+        <v>2078</v>
+      </c>
+      <c r="K117" s="25" t="n">
+        <v>24340</v>
+      </c>
+      <c r="L117" s="25" t="n">
+        <v>26774</v>
+      </c>
+      <c r="M117" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N117" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O117" s="32"/>
+      <c r="P117" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q117" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R117" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S117" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T117" s="23" t="s">
+        <v>2079</v>
+      </c>
+      <c r="U117" s="23"/>
+      <c r="V117" s="23"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B118" s="24" t="s">
+        <v>711</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>712</v>
+      </c>
+      <c r="D118" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E118" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F118" s="24" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G118" s="23" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="K118" s="25" t="n">
+        <v>3665</v>
+      </c>
+      <c r="L118" s="25" t="n">
+        <v>4031.5</v>
+      </c>
+      <c r="M118" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N118" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O118" s="32"/>
+      <c r="P118" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q118" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R118" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S118" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T118" s="23" t="s">
+        <v>2081</v>
+      </c>
+      <c r="U118" s="23"/>
+      <c r="V118" s="23"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D119" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E119" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F119" s="24" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G119" s="23" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H119" s="23"/>
+      <c r="I119" s="23"/>
+      <c r="J119" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="K119" s="25" t="n">
+        <v>1541.82</v>
+      </c>
+      <c r="L119" s="25" t="n">
+        <v>1696</v>
+      </c>
+      <c r="M119" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N119" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O119" s="32"/>
+      <c r="P119" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q119" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R119" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S119" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T119" s="23" t="s">
+        <v>2083</v>
+      </c>
+      <c r="U119" s="23"/>
+      <c r="V119" s="23"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="D120" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E120" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F120" s="24" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G120" s="23" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H120" s="23"/>
+      <c r="I120" s="23"/>
+      <c r="J120" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="K120" s="25" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L120" s="25" t="n">
+        <v>1191.3</v>
+      </c>
+      <c r="M120" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N120" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O120" s="32"/>
+      <c r="P120" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q120" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R120" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S120" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T120" s="23" t="s">
+        <v>2085</v>
+      </c>
+      <c r="U120" s="23"/>
+      <c r="V120" s="23"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="D121" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="E121" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F121" s="24" t="s">
+        <v>2086</v>
+      </c>
+      <c r="G121" s="23" t="s">
+        <v>2087</v>
+      </c>
+      <c r="H121" s="23"/>
+      <c r="I121" s="23"/>
+      <c r="J121" s="23" t="s">
+        <v>635</v>
+      </c>
+      <c r="K121" s="25" t="n">
+        <v>400</v>
+      </c>
+      <c r="L121" s="25" t="n">
+        <v>440</v>
+      </c>
+      <c r="M121" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N121" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O121" s="32"/>
+      <c r="P121" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q121" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R121" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S121" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T121" s="23" t="s">
+        <v>2088</v>
+      </c>
+      <c r="U121" s="23"/>
+      <c r="V121" s="23"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="23" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B122" s="24" t="s">
+        <v>747</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>748</v>
+      </c>
+      <c r="D122" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E122" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F122" s="24" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G122" s="23" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H122" s="23"/>
+      <c r="I122" s="23"/>
+      <c r="J122" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="K122" s="25" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="L122" s="25" t="n">
+        <v>136.51</v>
+      </c>
+      <c r="M122" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="N122" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="O122" s="32"/>
+      <c r="P122" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q122" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R122" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="S122" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="T122" s="23" t="s">
+        <v>2090</v>
+      </c>
+      <c r="U122" s="23"/>
+      <c r="V122" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:V116"/>
@@ -21808,54 +22196,54 @@
   <dimension ref="A1:V8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="A1" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -21925,9 +22313,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>113</v>
@@ -21950,7 +22338,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>2079</v>
+        <v>2093</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>-44.89</v>
@@ -21964,7 +22352,7 @@
       <c r="N3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="33"/>
+      <c r="O3" s="32"/>
       <c r="P3" s="26" t="s">
         <v>75</v>
       </c>
@@ -21978,14 +22366,14 @@
         <v>75</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>2080</v>
+        <v>2094</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>113</v>
@@ -22003,12 +22391,12 @@
         <v>252</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>2081</v>
+        <v>2095</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="23" t="s">
-        <v>2082</v>
+        <v>2096</v>
       </c>
       <c r="K4" s="25" t="n">
         <v>-6.05</v>
@@ -22022,7 +22410,7 @@
       <c r="N4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="26" t="s">
         <v>75</v>
       </c>
@@ -22036,14 +22424,14 @@
         <v>75</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>2083</v>
+        <v>2097</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>113</v>
@@ -22058,19 +22446,19 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>2084</v>
+        <v>2098</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2085</v>
+        <v>2099</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2086</v>
+        <v>2100</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>234</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2087</v>
+        <v>2101</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>6.05</v>
@@ -22100,14 +22488,14 @@
         <v>75</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>1858</v>
@@ -22125,14 +22513,14 @@
         <v>261</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>2090</v>
+        <v>2104</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="23" t="s">
-        <v>2091</v>
+        <v>2105</v>
       </c>
       <c r="K6" s="25" t="n">
         <v>15.66</v>
@@ -22146,7 +22534,7 @@
       <c r="N6" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O6" s="33"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="26" t="s">
         <v>75</v>
       </c>
@@ -22160,14 +22548,14 @@
         <v>77</v>
       </c>
       <c r="T6" s="23" t="s">
-        <v>2092</v>
+        <v>2106</v>
       </c>
       <c r="U6" s="23"/>
       <c r="V6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>113</v>
@@ -22182,15 +22570,15 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>2093</v>
+        <v>2107</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2094</v>
+        <v>2108</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>2079</v>
+        <v>2093</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>44.89</v>
@@ -22204,7 +22592,7 @@
       <c r="N7" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="26" t="s">
         <v>75</v>
       </c>
@@ -22218,14 +22606,14 @@
         <v>75</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>2095</v>
+        <v>2109</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>2078</v>
+        <v>2092</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>1858</v>
@@ -22243,14 +22631,14 @@
         <v>261</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>2089</v>
+        <v>2103</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>2090</v>
+        <v>2104</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23" t="s">
-        <v>2096</v>
+        <v>2110</v>
       </c>
       <c r="K8" s="25" t="n">
         <v>626.48</v>
@@ -22264,7 +22652,7 @@
       <c r="N8" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O8" s="33"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="26" t="s">
         <v>75</v>
       </c>
@@ -22278,7 +22666,7 @@
         <v>77</v>
       </c>
       <c r="T8" s="23" t="s">
-        <v>2097</v>
+        <v>2111</v>
       </c>
       <c r="U8" s="23"/>
       <c r="V8" s="23"/>
@@ -22307,54 +22695,54 @@
   <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="A1" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -22424,9 +22812,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>2099</v>
+        <v>2113</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>218</v>
@@ -22444,14 +22832,14 @@
         <v>210</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2100</v>
+        <v>2114</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2101</v>
+        <v>2115</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>2102</v>
+        <v>2116</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>480</v>
@@ -22465,26 +22853,26 @@
       <c r="N3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="33"/>
+      <c r="O3" s="32"/>
       <c r="P3" s="26" t="s">
         <v>75</v>
       </c>
       <c r="Q3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="R3" s="33"/>
+      <c r="R3" s="32"/>
       <c r="S3" s="26" t="s">
         <v>75</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>2103</v>
+        <v>2117</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>2099</v>
+        <v>2113</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>218</v>
@@ -22502,14 +22890,14 @@
         <v>1246</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>2104</v>
+        <v>2118</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>2101</v>
+        <v>2115</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="23" t="s">
-        <v>2102</v>
+        <v>2116</v>
       </c>
       <c r="K4" s="25" t="n">
         <v>1232</v>
@@ -22523,26 +22911,26 @@
       <c r="N4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="26" t="s">
         <v>75</v>
       </c>
       <c r="Q4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="R4" s="33"/>
+      <c r="R4" s="32"/>
       <c r="S4" s="26" t="s">
         <v>75</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>2105</v>
+        <v>2119</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>2099</v>
+        <v>2113</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>218</v>
@@ -22560,14 +22948,14 @@
         <v>1246</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2104</v>
+        <v>2118</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2101</v>
+        <v>2115</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>2102</v>
+        <v>2116</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>1232</v>
@@ -22581,19 +22969,19 @@
       <c r="N5" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="33"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="26" t="s">
         <v>75</v>
       </c>
       <c r="Q5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="33"/>
+      <c r="R5" s="32"/>
       <c r="S5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>2106</v>
+        <v>2120</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -22622,54 +23010,54 @@
   <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="A1" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -22739,9 +23127,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>2108</v>
+        <v>2122</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>113</v>
@@ -22759,14 +23147,14 @@
         <v>281</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2109</v>
+        <v>2123</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2110</v>
+        <v>2124</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>2111</v>
+        <v>2125</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>82.5</v>
@@ -22780,26 +23168,26 @@
       <c r="N3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="33"/>
+      <c r="O3" s="32"/>
       <c r="P3" s="26" t="s">
         <v>75</v>
       </c>
       <c r="Q3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="R3" s="33"/>
+      <c r="R3" s="32"/>
       <c r="S3" s="26" t="s">
         <v>75</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>2112</v>
+        <v>2126</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>2108</v>
+        <v>2122</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>129</v>
@@ -22817,14 +23205,14 @@
         <v>1299</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>2113</v>
+        <v>2127</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>2114</v>
+        <v>2128</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="23" t="s">
-        <v>2115</v>
+        <v>2129</v>
       </c>
       <c r="K4" s="25" t="n">
         <v>3600</v>
@@ -22838,26 +23226,26 @@
       <c r="N4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="Q4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="33"/>
+      <c r="R4" s="32"/>
       <c r="S4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>2116</v>
+        <v>2130</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>2108</v>
+        <v>2122</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>1705</v>
@@ -22872,17 +23260,17 @@
         <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>2117</v>
+        <v>2131</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2118</v>
+        <v>2132</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2119</v>
+        <v>2133</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>2120</v>
+        <v>2134</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>3888</v>
@@ -22896,19 +23284,19 @@
       <c r="N5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O5" s="33"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="Q5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="33"/>
+      <c r="R5" s="32"/>
       <c r="S5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>2121</v>
+        <v>2135</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -22937,54 +23325,54 @@
   <dimension ref="A1:V9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
+      <c r="A1" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -23054,9 +23442,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>2123</v>
+        <v>2137</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1420</v>
@@ -23074,14 +23462,14 @@
         <v>734</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2124</v>
+        <v>2138</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2125</v>
+        <v>2139</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>2126</v>
+        <v>2140</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>-2812.73</v>
@@ -23093,7 +23481,7 @@
       <c r="N3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="33"/>
+      <c r="O3" s="32"/>
       <c r="P3" s="26" t="s">
         <v>75</v>
       </c>
@@ -23107,20 +23495,20 @@
         <v>77</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>2127</v>
+        <v>2141</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>2128</v>
+        <v>2142</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>2129</v>
+        <v>2143</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>2130</v>
+        <v>2144</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>136</v>
@@ -23132,14 +23520,14 @@
         <v>1180</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>2131</v>
+        <v>2145</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>2125</v>
+        <v>2139</v>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="23" t="s">
-        <v>2132</v>
+        <v>2146</v>
       </c>
       <c r="K4" s="25" t="n">
         <v>-2159</v>
@@ -23153,7 +23541,7 @@
       <c r="N4" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="33"/>
+      <c r="O4" s="32"/>
       <c r="P4" s="26" t="s">
         <v>75</v>
       </c>
@@ -23167,20 +23555,20 @@
         <v>75</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>2133</v>
+        <v>2147</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>2128</v>
+        <v>2142</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2129</v>
+        <v>2143</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2130</v>
+        <v>2144</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>136</v>
@@ -23189,17 +23577,17 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>2134</v>
+        <v>2148</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2135</v>
+        <v>2149</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2125</v>
+        <v>2139</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>2136</v>
+        <v>2150</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>-1552.73</v>
@@ -23213,7 +23601,7 @@
       <c r="N5" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O5" s="33"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="26" t="s">
         <v>75</v>
       </c>
@@ -23227,14 +23615,14 @@
         <v>75</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>2137</v>
+        <v>2151</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>2123</v>
+        <v>2137</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>1420</v>
@@ -23252,14 +23640,14 @@
         <v>539</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>2138</v>
+        <v>2152</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>2125</v>
+        <v>2139</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="23" t="s">
-        <v>2139</v>
+        <v>2153</v>
       </c>
       <c r="K6" s="25" t="n">
         <v>-204.55</v>
@@ -23271,7 +23659,7 @@
       <c r="N6" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O6" s="33"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="26" t="s">
         <v>75</v>
       </c>
@@ -23285,20 +23673,20 @@
         <v>77</v>
       </c>
       <c r="T6" s="23" t="s">
-        <v>2140</v>
+        <v>2154</v>
       </c>
       <c r="U6" s="23"/>
       <c r="V6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>2128</v>
+        <v>2142</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2129</v>
+        <v>2143</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2130</v>
+        <v>2144</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>136</v>
@@ -23310,12 +23698,12 @@
         <v>1787</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>2136</v>
+        <v>2150</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>1552.73</v>
@@ -23329,7 +23717,7 @@
       <c r="N7" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="33"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="26" t="s">
         <v>75</v>
       </c>
@@ -23343,14 +23731,14 @@
         <v>77</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>2142</v>
+        <v>2156</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>2123</v>
+        <v>2137</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>1304</v>
@@ -23368,14 +23756,14 @@
         <v>517</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>2143</v>
+        <v>2157</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>2125</v>
+        <v>2139</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23" t="s">
-        <v>2144</v>
+        <v>2158</v>
       </c>
       <c r="K8" s="25" t="n">
         <v>1878</v>
@@ -23389,7 +23777,7 @@
       <c r="N8" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="O8" s="33"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="26" t="s">
         <v>75</v>
       </c>
@@ -23403,20 +23791,20 @@
         <v>75</v>
       </c>
       <c r="T8" s="23" t="s">
-        <v>2145</v>
+        <v>2159</v>
       </c>
       <c r="U8" s="23"/>
       <c r="V8" s="23"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>2128</v>
+        <v>2142</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2129</v>
+        <v>2143</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2130</v>
+        <v>2144</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>136</v>
@@ -23428,12 +23816,12 @@
         <v>1787</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>2132</v>
+        <v>2146</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>2159</v>
@@ -23447,7 +23835,7 @@
       <c r="N9" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="33"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="26" t="s">
         <v>75</v>
       </c>
@@ -23461,7 +23849,7 @@
         <v>77</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>2146</v>
+        <v>2160</v>
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
